--- a/data/trans_orig/P79A3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79A3_2023-Edad-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>889</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>889</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>889</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>889</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>758</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>76,34%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>676</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>941</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>596</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>596</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>596</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>33223</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
